--- a/projeto_horto/conecta/static/conecta/files/Materiais.xlsx
+++ b/projeto_horto/conecta/static/conecta/files/Materiais.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>nome_aula</t>
   </si>
@@ -70,6 +70,78 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1fP1E2PN1ZryF77Iw3JOQs_v7k8CG_Hn6/edit</t>
+  </si>
+  <si>
+    <t>Aula 5 - Power Point II.pptx</t>
+  </si>
+  <si>
+    <t>Aula 5 - Orientação - Power Point II.docx</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1HXa4wZJuYdcJrZhwf5VyNOKbnFAwzp5b/edit?rtpof=true</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1JdpjzgZ7xKEUgXYM87BDR_6eof9w09OC/edit</t>
+  </si>
+  <si>
+    <t>Aula 6 - Excel I .pptx</t>
+  </si>
+  <si>
+    <t>Aula 6 - Orientação - Excel I.docx</t>
+  </si>
+  <si>
+    <t>Aula 8 - Orientação - Excel III.docx</t>
+  </si>
+  <si>
+    <t>Aula 8 - Excel III .pptx</t>
+  </si>
+  <si>
+    <t>Aula 7 - Orientação - Excel II.docx</t>
+  </si>
+  <si>
+    <t>Aula 7 - Excel II .pptx</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1ut2ZwhhPkysShdIHDDG8yH50c3qiIeMn/edit?rtpof=true</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1Is6fNSn76lpNnsKiuzfO-0P0nZb-EfpL/edit?rtpof=true&amp;tab=t.0</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1CAu_NjsuskM4rlC_NBbP_y6feddadrAv/edit</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1qgk9-MT3BU0_KFY0I8AL3t2LE-7YeBlZ/edit</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1xOKx_0-5x37MIifEt1J89GO0wcSry0BR/edit?rtpof=true</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1B-8cZdzNVAvCOD_NVczRn3dO3BfvbG_7/edit?rtpof=true&amp;tab=t.0</t>
+  </si>
+  <si>
+    <t>Aula 9 - Ferramentas Google.pptx</t>
+  </si>
+  <si>
+    <t>Aula 9 - Orientação - Ferramentas Google.docx</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1HVIrkjLPQ4hfeGGAFvDyTC7V9m-JoC66/edit?rtpof=true</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1qbqc8kiDkQ9UG5E_cmA0RWsM_Mx_ZSv0/edit</t>
+  </si>
+  <si>
+    <t>Aula 10 - IA/Browser.pptx</t>
+  </si>
+  <si>
+    <t>Aula 10 - Orientação - IA/Browser.docx</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1LjJ8AUD8IYgblvLsmGiky6Gr4gj-qt5Y/edit</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/17REykVwK5kZWDrDxCILCHkul-7KPCqkV/edit</t>
   </si>
 </sst>
 </file>
@@ -414,11 +486,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -493,9 +565,105 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/projeto_horto/conecta/static/conecta/files/Materiais.xlsx
+++ b/projeto_horto/conecta/static/conecta/files/Materiais.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>nome_aula</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/17REykVwK5kZWDrDxCILCHkul-7KPCqkV/edit</t>
+  </si>
+  <si>
+    <t>Revisão</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1WwlhDHsJMpbbasxgQRvIytWGQ5iPkf8L/edit?slide=id.p1#slide=id.p1</t>
   </si>
 </sst>
 </file>
@@ -486,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="57.6640625" bestFit="1" customWidth="1"/>
@@ -659,6 +665,14 @@
       </c>
       <c r="B21" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
